--- a/artfynd/A 8707-2025 artfynd.xlsx
+++ b/artfynd/A 8707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118308273</v>
+        <v>113120990</v>
       </c>
       <c r="B2" t="n">
-        <v>97853</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårdsjön, Jmt</t>
+          <t>Öretjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527248</v>
+        <v>527205</v>
       </c>
       <c r="R2" t="n">
-        <v>6981202</v>
+        <v>6980954</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118308270</v>
+        <v>118308272</v>
       </c>
       <c r="B3" t="n">
-        <v>78228</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527322</v>
+        <v>527263</v>
       </c>
       <c r="R3" t="n">
-        <v>6981250</v>
+        <v>6981222</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +873,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118308268</v>
+        <v>118308269</v>
       </c>
       <c r="B4" t="n">
-        <v>97752</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219795</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,7 +908,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527319</v>
+        <v>527322</v>
       </c>
       <c r="R4" t="n">
         <v>6981250</v>
@@ -981,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118308269</v>
+        <v>118308275</v>
       </c>
       <c r="B5" t="n">
-        <v>80448</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527322</v>
+        <v>527160</v>
       </c>
       <c r="R5" t="n">
-        <v>6981250</v>
+        <v>6980918</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,16 +1070,11 @@
         <v>118308274</v>
       </c>
       <c r="B6" t="n">
-        <v>78491</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1188,12 +1167,7 @@
         <v>118308271</v>
       </c>
       <c r="B7" t="n">
-        <v>78227</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,37 +1261,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118308275</v>
+        <v>118308268</v>
       </c>
       <c r="B8" t="n">
-        <v>90511</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>219795</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527160</v>
+        <v>527319</v>
       </c>
       <c r="R8" t="n">
-        <v>6980918</v>
+        <v>6981250</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,37 +1358,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118308272</v>
+        <v>118308273</v>
       </c>
       <c r="B9" t="n">
-        <v>91266</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527263</v>
+        <v>527248</v>
       </c>
       <c r="R9" t="n">
-        <v>6981222</v>
+        <v>6981202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,6 +1452,103 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118308270</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gårdsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>527322</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6981250</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8707-2025 artfynd.xlsx
+++ b/artfynd/A 8707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120990</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308272</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308269</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308275</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308274</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308271</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308268</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308273</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,8 +1594,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308270</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>